--- a/docs/sample-output/14-master-planned-3-phase/proforma.xlsx
+++ b/docs/sample-output/14-master-planned-3-phase/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -8.68% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -8.01% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Brazos Crossing — 3-phase master plan · 5-Year Before-Tax</t>
@@ -1073,7 +1073,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.04537422347321264</v>
+        <v>0.04575557971308636</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>60717024.43525998</v>
+        <v>60210969.95446999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>-0.08679040891597671</v>
+        <v>-0.08010698187010867</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.6220594003476227</v>
+        <v>0.6473736408597348</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>-0.08679040891597671</v>
+        <v>-0.08010698187010867</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>1107042.52126</v>
+        <v>1097815.72147</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>170314234.04</v>
+        <v>168894726.38</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-110704252.126</v>
+        <v>-109781572.147</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>60717024.43525998</v>
+        <v>60210969.95446999</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>10.56277809724634</v>
+        <v>10.474741154800297</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>287.59580216143195</v>
+        <v>285.1987949679162</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>110704252.126</v>
+        <v>109781572.147</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>747483.0382711008</v>
+        <v>741253.036976572</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>8969796.45925321</v>
+        <v>8895036.443718864</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,19 +1490,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-8969796.45925321</v>
+        <v>-8895036.443718864</v>
       </c>
       <c r="C13" s="16">
-        <v>-8969796.45925321</v>
+        <v>-8895036.443718864</v>
       </c>
       <c r="D13" s="16">
-        <v>-8969796.45925321</v>
+        <v>-8895036.443718864</v>
       </c>
       <c r="E13" s="16">
-        <v>-8969796.45925321</v>
+        <v>-8895036.443718864</v>
       </c>
       <c r="F13" s="16">
-        <v>-8969796.45925321</v>
+        <v>-8895036.443718864</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,19 +1510,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-1241920.3432532111</v>
+        <v>-1167160.3277188642</v>
       </c>
       <c r="C14" s="18">
-        <v>-1010084.0597732104</v>
+        <v>-935324.0442388635</v>
       </c>
       <c r="D14" s="18">
-        <v>-771292.6877888124</v>
+        <v>-696532.6722544655</v>
       </c>
       <c r="E14" s="18">
-        <v>-525337.5746448785</v>
+        <v>-450577.5591105316</v>
       </c>
       <c r="F14" s="18">
-        <v>-272003.8081066273</v>
+        <v>-197243.7925722804</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,19 +1666,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-108876415.05448021</v>
+        <v>-107968969.43765128</v>
       </c>
       <c r="C9" s="16">
-        <v>-106926164.34912182</v>
+        <v>-106034973.36791265</v>
       </c>
       <c r="D9" s="16">
-        <v>-104845301.74215633</v>
+        <v>-103971453.99961796</v>
       </c>
       <c r="E9" s="16">
-        <v>-102625079.91263951</v>
+        <v>-101769736.91758549</v>
       </c>
       <c r="F9" s="16">
-        <v>-100256165.71534348</v>
+        <v>-99420566.76498365</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,19 +1686,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>17152484.94551979</v>
+        <v>18059930.562348723</v>
       </c>
       <c r="C10" s="18">
-        <v>22883735.650878176</v>
+        <v>23774926.63208735</v>
       </c>
       <c r="D10" s="18">
-        <v>28858648.257843673</v>
+        <v>29732496.000382036</v>
       </c>
       <c r="E10" s="18">
-        <v>35089770.08736049</v>
+        <v>35945113.08241451</v>
       </c>
       <c r="F10" s="18">
-        <v>41590234.284656525</v>
+        <v>42425833.235016346</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,19 +1736,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.8207053644184484</v>
+        <v>0.8138650814675739</v>
       </c>
       <c r="C13" s="21">
-        <v>0.7825278051340131</v>
+        <v>0.776005718358284</v>
       </c>
       <c r="D13" s="21">
-        <v>0.7449520874667391</v>
+        <v>0.7387431807335315</v>
       </c>
       <c r="E13" s="21">
-        <v>0.7079398185236199</v>
+        <v>0.7020393956912142</v>
       </c>
       <c r="F13" s="21">
-        <v>0.671454174583044</v>
+        <v>0.6658578464221473</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,19 +1756,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.8615442001504894</v>
+        <v>0.8687852112688035</v>
       </c>
       <c r="C14" s="22">
-        <v>0.8873905261550042</v>
+        <v>0.8948487676068677</v>
       </c>
       <c r="D14" s="22">
-        <v>0.9140122419396541</v>
+        <v>0.9216942306350735</v>
       </c>
       <c r="E14" s="22">
-        <v>0.9414326091978439</v>
+        <v>0.9493450575541259</v>
       </c>
       <c r="F14" s="22">
-        <v>0.9696755874737794</v>
+        <v>0.9778254092807498</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1776,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.06980649765109637</v>
+        <v>0.0703931995585944</v>
       </c>
       <c r="C15" s="21">
-        <v>0.07190069258062927</v>
+        <v>0.07250499554535224</v>
       </c>
       <c r="D15" s="21">
-        <v>0.07405771335804813</v>
+        <v>0.07468014541171278</v>
       </c>
       <c r="E15" s="21">
-        <v>0.07627944475878959</v>
+        <v>0.07692054977406419</v>
       </c>
       <c r="F15" s="21">
-        <v>0.07856782810155329</v>
+        <v>0.07922816626728613</v>
       </c>
     </row>
   </sheetData>
@@ -1864,19 +1864,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.020454235938017987</v>
+        <v>-0.01938451296502018</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.016635928212361935</v>
+        <v>-0.015534113550174193</v>
       </c>
       <c r="D5" s="21">
-        <v>-0.01270307125493624</v>
+        <v>-0.01156820215288287</v>
       </c>
       <c r="E5" s="21">
-        <v>-0.008652228588787713</v>
+        <v>-0.007483313413672739</v>
       </c>
       <c r="F5" s="21">
-        <v>-0.00447986064265474</v>
+        <v>-0.003275878012286318</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,19 +1884,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>-0.07240468930291055</v>
+        <v>-0.06462706618330835</v>
       </c>
       <c r="C6" s="21">
-        <v>-0.044139823811259936</v>
+        <v>-0.03934077520880852</v>
       </c>
       <c r="D6" s="21">
-        <v>-0.026726570173957402</v>
+        <v>-0.023426646462695756</v>
       </c>
       <c r="E6" s="21">
-        <v>-0.014971245845640573</v>
+        <v>-0.012535154864513932</v>
       </c>
       <c r="F6" s="21">
-        <v>-0.0065400883833678</v>
+        <v>-0.0046491436356631026</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,19 +1904,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.2620445377594442</v>
+        <v>0.28055967620856703</v>
       </c>
       <c r="C7" s="23">
-        <v>0.33980142208468245</v>
+        <v>0.3599417560706591</v>
       </c>
       <c r="D7" s="23">
-        <v>0.4255042371942253</v>
+        <v>0.447318469982069</v>
       </c>
       <c r="E7" s="23">
-        <v>0.5194776212317743</v>
+        <v>0.5430159737306226</v>
       </c>
       <c r="F7" s="23">
-        <v>0.6220594003476227</v>
+        <v>0.6473736408597348</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,19 +1924,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.21464710879864868</v>
+        <v>-0.208046461942178</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.07763018648149668</v>
+        <v>-0.07366422830849162</v>
       </c>
       <c r="D8" s="21">
-        <v>-0.0268360431795164</v>
+        <v>-0.02398106908402066</v>
       </c>
       <c r="E8" s="21">
-        <v>-0.0004243377709949181</v>
+        <v>0.0018262552347825898</v>
       </c>
       <c r="F8" s="21">
-        <v>0.015741373455562417</v>
+        <v>0.01761319514450919</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,19 +1964,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.7379554622403118</v>
+        <v>-0.7194403237913272</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.40992698306586195</v>
+        <v>-0.3937213084085489</v>
       </c>
       <c r="D10" s="24">
-        <v>-0.24047164839888518</v>
+        <v>-0.22876857951618404</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.14536120507404177</v>
+        <v>-0.13669475080137622</v>
       </c>
       <c r="F10" s="24">
-        <v>-0.08679040891597671</v>
+        <v>-0.08010698187010867</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.5234</v>
+        <v>-0.5114000000000001</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.3323</v>
+        <v>-0.32</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.2137</v>
+        <v>-0.2048</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.145</v>
+        <v>-0.13849999999999998</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.10250000000000001</v>
+        <v>-0.09770000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2090,19 +2090,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>153282811</v>
+        <v>152005254</v>
       </c>
       <c r="C6" s="18">
-        <v>161798522</v>
+        <v>160449990</v>
       </c>
       <c r="D6" s="18">
-        <v>170314234</v>
+        <v>168894726</v>
       </c>
       <c r="E6" s="18">
-        <v>178829946</v>
+        <v>177339463</v>
       </c>
       <c r="F6" s="18">
-        <v>187345657</v>
+        <v>185784199</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.05041580373940297</v>
+        <v>0.05083953292824996</v>
       </c>
       <c r="C7" s="21">
-        <v>0.04776234059789495</v>
+        <v>0.04816376813734921</v>
       </c>
       <c r="D7" s="21">
-        <v>0.045374223483869235</v>
+        <v>0.04575557981603286</v>
       </c>
       <c r="E7" s="21">
-        <v>0.043213546102619745</v>
+        <v>0.04357674250992854</v>
       </c>
       <c r="F7" s="21">
-        <v>0.04124929416431575</v>
+        <v>0.04159598156138133</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,19 +2130,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>99633827.15</v>
+        <v>98803415.10000001</v>
       </c>
       <c r="C8" s="16">
-        <v>105169039.3</v>
+        <v>104292493.5</v>
       </c>
       <c r="D8" s="16">
-        <v>110704252.10000001</v>
+        <v>109781571.9</v>
       </c>
       <c r="E8" s="16">
-        <v>116239464.9</v>
+        <v>115270650.95</v>
       </c>
       <c r="F8" s="16">
-        <v>121774677.05</v>
+        <v>120759729.35000001</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,19 +2150,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>54645322.121499985</v>
+        <v>54189873.050999984</v>
       </c>
       <c r="C9" s="16">
-        <v>57681173.09300001</v>
+        <v>57200421.435</v>
       </c>
       <c r="D9" s="16">
-        <v>60717024.42099999</v>
+        <v>60210969.819000006</v>
       </c>
       <c r="E9" s="16">
-        <v>63752875.74899998</v>
+        <v>63221518.559499994</v>
       </c>
       <c r="F9" s="16">
-        <v>66788726.72050001</v>
+        <v>66232066.9435</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,19 +2170,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.05041580373940297</v>
+        <v>0.05083953292824996</v>
       </c>
       <c r="C10" s="21">
-        <v>0.04776234059789495</v>
+        <v>0.04816376813734921</v>
       </c>
       <c r="D10" s="21">
-        <v>0.045374223483869235</v>
+        <v>0.04575557981603286</v>
       </c>
       <c r="E10" s="21">
-        <v>0.043213546102619745</v>
+        <v>0.04357674250992854</v>
       </c>
       <c r="F10" s="21">
-        <v>0.04124929416431575</v>
+        <v>0.04159598156138133</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,19 +2190,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.05192827785158507</v>
+        <v>0.052364718916097466</v>
       </c>
       <c r="C11" s="21">
-        <v>0.0491952108158318</v>
+        <v>0.04960868118146969</v>
       </c>
       <c r="D11" s="21">
-        <v>0.04673545018838531</v>
+        <v>0.04712824721051385</v>
       </c>
       <c r="E11" s="21">
-        <v>0.04450995248569834</v>
+        <v>0.0448840447852264</v>
       </c>
       <c r="F11" s="21">
-        <v>0.04248677298924522</v>
+        <v>0.042843861008222774</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,19 +2210,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.05348612618713261</v>
+        <v>0.05393566048358038</v>
       </c>
       <c r="C12" s="21">
-        <v>0.050671067140306746</v>
+        <v>0.05109694161691377</v>
       </c>
       <c r="D12" s="21">
-        <v>0.04813751369403686</v>
+        <v>0.04854209462682925</v>
       </c>
       <c r="E12" s="21">
-        <v>0.04584525106026928</v>
+        <v>0.04623056612878318</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04376137617892257</v>
+        <v>0.044129176838469446</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,19 +2230,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.0550907099727466</v>
+        <v>0.0555537302980878</v>
       </c>
       <c r="C13" s="21">
-        <v>0.05219119915451596</v>
+        <v>0.05262984986542119</v>
       </c>
       <c r="D13" s="21">
-        <v>0.04958163910485798</v>
+        <v>0.049998357465634136</v>
       </c>
       <c r="E13" s="21">
-        <v>0.04722060859207737</v>
+        <v>0.047617483112646686</v>
       </c>
       <c r="F13" s="21">
-        <v>0.04507421746429026</v>
+        <v>0.04545305214362354</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2250,19 +2250,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.056743431271929004</v>
+        <v>0.05722034220703044</v>
       </c>
       <c r="C14" s="21">
-        <v>0.053756935129151445</v>
+        <v>0.054208745361383835</v>
       </c>
       <c r="D14" s="21">
-        <v>0.05106908827800372</v>
+        <v>0.051498308189603166</v>
       </c>
       <c r="E14" s="21">
-        <v>0.0486372268498397</v>
+        <v>0.04904600760602609</v>
       </c>
       <c r="F14" s="21">
-        <v>0.04642644398821897</v>
+        <v>0.04681664370793225</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,19 +2270,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>-0.006312355808451838</v>
+        <v>-0.00512377463356546</v>
       </c>
       <c r="C15" s="21">
-        <v>-0.01375545017453324</v>
+        <v>-0.012629426220944819</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.020454235908125732</v>
+        <v>-0.019384512676250198</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.026515042026637625</v>
+        <v>-0.025496258275420777</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.03202486513548473</v>
+        <v>-0.03105238996840036</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,19 +2290,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>-0.002069791678908797</v>
+        <v>-0.0008455530687758275</v>
       </c>
       <c r="C16" s="21">
-        <v>-0.009736178875972641</v>
+        <v>-0.00857637420377657</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.01663592818157291</v>
+        <v>-0.01553411325274111</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.02287855848364016</v>
+        <v>-0.021829211219886804</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.02855367628575268</v>
+        <v>-0.02755202686365578</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,19 +2310,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>0.002300049374520486</v>
+        <v>0.003561015142957444</v>
       </c>
       <c r="C17" s="21">
-        <v>-0.005596329438455274</v>
+        <v>-0.004401730626093322</v>
       </c>
       <c r="D17" s="21">
-        <v>-0.012703071223223549</v>
+        <v>-0.011568201846526795</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.01913298043435281</v>
+        <v>-0.01805215275268686</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.024978351770528706</v>
+        <v>-0.0239466528657689</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,19 +2330,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>0.0068009856595527204</v>
+        <v>0.008099780401042787</v>
       </c>
       <c r="C18" s="21">
-        <v>-0.0013322845178123169</v>
+        <v>-0.00010184774107950557</v>
       </c>
       <c r="D18" s="21">
-        <v>-0.008652228556123638</v>
+        <v>-0.007483313098125984</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.015275035043586781</v>
+        <v>-0.014161782531470851</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.021295767519847957</v>
+        <v>-0.020233117647945352</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2350,19 +2350,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>0.011436950033135908</v>
+        <v>0.012774708616870677</v>
       </c>
       <c r="C19" s="21">
-        <v>0.0030596817504499165</v>
+        <v>0.004327031630484712</v>
       </c>
       <c r="D19" s="21">
-        <v>-0.004479860609010744</v>
+        <v>-0.0032758776872731615</v>
       </c>
       <c r="E19" s="21">
-        <v>-0.01130135129109778</v>
+        <v>-0.010154701203618376</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.017502705741646793</v>
+        <v>-0.016408176373587113</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,19 +2370,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>-0.12738567851554064</v>
+        <v>-0.12005162587325738</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.17331274437729044</v>
+        <v>-0.16636469646401952</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.21464710861500297</v>
+        <v>-0.20804646016012426</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.25204486660151626</v>
+        <v>-0.24575853646320403</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.2860428244892348</v>
+        <v>-0.2800422380596348</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,19 +2390,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>-0.02640976113608314</v>
+        <v>-0.022217978484350684</v>
       </c>
       <c r="C21" s="21">
-        <v>-0.05304840682103058</v>
+        <v>-0.048974143136455664</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.07763018637071477</v>
+        <v>-0.07366422723981608</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.1004061064480071</v>
+        <v>-0.09654038018404623</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.12158634811458337</v>
+        <v>-0.11781373027413242</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2410,19 +2410,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.009769959623770993</v>
+        <v>0.012740868394423645</v>
       </c>
       <c r="C22" s="21">
-        <v>-0.009196837355169789</v>
+        <v>-0.006286102137402617</v>
       </c>
       <c r="D22" s="21">
-        <v>-0.026836043099333948</v>
+        <v>-0.023981068315467625</v>
       </c>
       <c r="E22" s="21">
-        <v>-0.04330135804322796</v>
+        <v>-0.04049826364590187</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.05872232879801655</v>
+        <v>-0.05596767593824188</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2430,19 +2430,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.02833911177890483</v>
+        <v>0.03066484489606425</v>
       </c>
       <c r="C23" s="21">
-        <v>0.013460836904890222</v>
+        <v>0.015747581156558284</v>
       </c>
       <c r="D23" s="21">
-        <v>-0.0004243377079987676</v>
+        <v>0.0018262558406765342</v>
       </c>
       <c r="E23" s="21">
-        <v>-0.013428848503693202</v>
+        <v>-0.011211913139277533</v>
       </c>
       <c r="F23" s="21">
-        <v>-0.0256476912064552</v>
+        <v>-0.023462206252752388</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,19 +2450,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.03962472489413407</v>
+        <v>0.04155223763609388</v>
       </c>
       <c r="C24" s="21">
-        <v>0.027281271711724564</v>
+        <v>0.02917986821886312</v>
       </c>
       <c r="D24" s="21">
-        <v>0.015741373508214425</v>
+        <v>0.01761319564827082</v>
       </c>
       <c r="E24" s="21">
-        <v>0.004914915975486333</v>
+        <v>0.006761839540990857</v>
       </c>
       <c r="F24" s="21">
-        <v>-0.005274295732296586</v>
+        <v>-0.00345061312092007</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,19 +2470,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.4931828667751989</v>
+        <v>-0.47261048909761116</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.6220105410013885</v>
+        <v>-0.6025209255363995</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.7379554617230778</v>
+        <v>-0.7194403187934442</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.8428580086723224</v>
+        <v>-0.825224544047104</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.9382239494494293</v>
+        <v>-0.9213920099553021</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,19 +2490,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>-0.22060800929196944</v>
+        <v>-0.2065921595821479</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.3142549234919395</v>
+        <v>-0.29935414766286905</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.40992698260762905</v>
+        <v>-0.39372130408706607</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.5108814738608973</v>
+        <v>-0.49262224842829105</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.6232843904578846</v>
+        <v>-0.6013319238884702</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,19 +2510,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>-0.10564303556921363</v>
+        <v>-0.09584412577805995</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.17178722914027028</v>
+        <v>-0.16118618125243597</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.24047164806738208</v>
+        <v>-0.22876857639934448</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.31379479319200243</v>
+        <v>-0.30049978985156534</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.3952680717700562</v>
+        <v>-0.37947557965642026</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,19 +2530,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>-0.045068192147645035</v>
+        <v>-0.03776087072878967</v>
       </c>
       <c r="C28" s="21">
-        <v>-0.09436195192423277</v>
+        <v>-0.086468510170525</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.1453612048293133</v>
+        <v>-0.13669474849126803</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.19929688433922638</v>
+        <v>-0.18957489746683115</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.25801451348822496</v>
+        <v>-0.246773438993992</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2550,19 +2550,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>-0.008774678339180114</v>
+        <v>-0.0030449930347011414</v>
       </c>
       <c r="C29" s="21">
-        <v>-0.047285069994092356</v>
+        <v>-0.04113695769930551</v>
       </c>
       <c r="D29" s="21">
-        <v>-0.08679040872686757</v>
+        <v>-0.08010698008671963</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.12803544859174174</v>
+        <v>-0.12065092261667418</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.17203884099839822</v>
+        <v>-0.16370394812490596</v>
       </c>
     </row>
   </sheetData>
